--- a/data/trans_orig/ED_INF-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Habitat-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,36</t>
+          <t>7,11; 8,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 8,21</t>
+          <t>6,91; 8,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 8,52</t>
+          <t>7,21; 8,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 9,97</t>
+          <t>8,73; 10,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,76</t>
+          <t>7,41; 8,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,21</t>
+          <t>7,0; 8,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,07</t>
+          <t>6,79; 8,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,02; 11,09</t>
+          <t>9,11; 11,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,37</t>
+          <t>7,46; 8,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,98</t>
+          <t>7,06; 7,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,11</t>
+          <t>7,18; 8,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 10,32</t>
+          <t>9,06; 10,39</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 8,64</t>
+          <t>7,5; 8,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,89</t>
+          <t>6,83; 7,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,14</t>
+          <t>7,15; 8,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 10,23</t>
+          <t>9,11; 10,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 8,25</t>
+          <t>7,23; 8,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,75</t>
+          <t>6,74; 7,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,99</t>
+          <t>6,99; 7,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 9,98</t>
+          <t>8,94; 9,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,28</t>
+          <t>7,54; 8,27</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,7</t>
+          <t>6,92; 7,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,94</t>
+          <t>7,19; 7,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 9,9</t>
+          <t>9,18; 9,92</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 8,26</t>
+          <t>6,95; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,65</t>
+          <t>6,45; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,96</t>
+          <t>6,84; 7,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,09</t>
+          <t>9,17; 12,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,77; 8,02</t>
+          <t>6,8; 8,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 7,51</t>
+          <t>6,4; 7,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 8,11</t>
+          <t>7,02; 8,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,25; 10,55</t>
+          <t>9,3; 10,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,96</t>
+          <t>7,07; 7,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 7,4</t>
+          <t>6,6; 7,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,88</t>
+          <t>7,11; 7,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,49; 11,12</t>
+          <t>9,43; 11,23</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 7,87</t>
+          <t>6,82; 7,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 7,79</t>
+          <t>6,65; 7,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,94</t>
+          <t>6,91; 7,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 9,73</t>
+          <t>8,6; 9,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,03</t>
+          <t>6,99; 8,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,88</t>
+          <t>6,78; 7,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 8,33</t>
+          <t>7,29; 8,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 9,73</t>
+          <t>8,63; 9,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,81</t>
+          <t>7,08; 7,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,66</t>
+          <t>6,87; 7,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,95</t>
+          <t>7,21; 7,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 9,6</t>
+          <t>8,74; 9,51</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,01</t>
+          <t>7,41; 7,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,57</t>
+          <t>6,99; 7,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,86</t>
+          <t>7,29; 7,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,26; 10,26</t>
+          <t>9,22; 10,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,98</t>
+          <t>7,43; 7,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,55</t>
+          <t>6,97; 7,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,84</t>
+          <t>7,29; 7,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,9</t>
+          <t>9,24; 9,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,88</t>
+          <t>7,49; 7,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,47</t>
+          <t>7,05; 7,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,76</t>
+          <t>7,36; 7,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,33; 9,95</t>
+          <t>9,36; 9,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_INF-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Habitat-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,09</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,56</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,43</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,03</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,74</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,54</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,86</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,43</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,87</t>
+          <t>9,6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>9,82</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,44</t>
+          <t>7,41; 8,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,24</t>
+          <t>6,97; 8,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 8,54</t>
+          <t>6,75; 8,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,73; 10,0</t>
+          <t>9,32; 11,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,73</t>
+          <t>7,11; 8,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 8,18</t>
+          <t>6,9; 8,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,07</t>
+          <t>7,14; 8,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 11,09</t>
+          <t>8,99; 10,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,39</t>
+          <t>7,44; 8,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,99</t>
+          <t>7,11; 8,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 8,1</t>
+          <t>7,14; 8,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 10,39</t>
+          <t>9,35; 10,43</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,73</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,26</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,48</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,69</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,08</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,35</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,63</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,73</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,48</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,41</t>
+          <t>9,8</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,51</t>
+          <t>9,74</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,59</t>
+          <t>7,2; 8,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,86</t>
+          <t>6,81; 7,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 8,09</t>
+          <t>7,03; 8,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 10,34</t>
+          <t>9,25; 10,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,21</t>
+          <t>7,56; 8,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 7,74</t>
+          <t>6,83; 7,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,95</t>
+          <t>7,1; 8,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 9,99</t>
+          <t>9,32; 10,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,27</t>
+          <t>7,52; 8,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,64</t>
+          <t>6,94; 7,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,91</t>
+          <t>7,18; 7,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 9,92</t>
+          <t>9,39; 10,08</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,92</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,54</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,21</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,05</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,42</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,16</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,9</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,03</t>
+          <t>9,95</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,22</t>
+          <t>6,86; 8,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,64</t>
+          <t>6,36; 7,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,94</t>
+          <t>7,01; 8,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,08</t>
+          <t>9,65; 10,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 8,04</t>
+          <t>7,0; 8,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 7,49</t>
+          <t>6,5; 7,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,11</t>
+          <t>6,84; 7,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 10,57</t>
+          <t>9,15; 10,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,95</t>
+          <t>7,14; 7,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,44</t>
+          <t>6,57; 7,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,89</t>
+          <t>7,06; 7,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 11,23</t>
+          <t>9,57; 10,39</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,52</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,76</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,29</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,19</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,42</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,13</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,52</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,76</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,18</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,16</t>
+          <t>9,36</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,9</t>
+          <t>6,94; 8,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,74</t>
+          <t>6,78; 7,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,93</t>
+          <t>7,18; 8,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,6; 9,7</t>
+          <t>8,72; 9,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,05</t>
+          <t>6,8; 7,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,85</t>
+          <t>6,63; 7,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,31</t>
+          <t>6,93; 7,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 9,78</t>
+          <t>8,86; 10,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,82</t>
+          <t>7,04; 7,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,62</t>
+          <t>6,83; 7,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,92</t>
+          <t>7,25; 7,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 9,51</t>
+          <t>8,97; 9,74</t>
         </is>
       </c>
     </row>
@@ -1208,62 +1208,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,69</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,26</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,56</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,78</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>7,7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,27</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7,69</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>7,26</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,56</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,71</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,97</t>
+          <t>7,39; 7,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,57</t>
+          <t>6,97; 7,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,84</t>
+          <t>7,3; 7,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 10,25</t>
+          <t>9,48; 10,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,99</t>
+          <t>7,44; 8,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,54</t>
+          <t>6,96; 7,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,83</t>
+          <t>7,27; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,91</t>
+          <t>9,34; 9,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,91</t>
+          <t>7,48; 7,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,44</t>
+          <t>7,06; 7,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,77</t>
+          <t>7,35; 7,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,96</t>
+          <t>9,52; 9,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_INF-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,43</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,03</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,74</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,86</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,93</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7,55</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7,63</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,82</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>8.094947735727898</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7.55970296951666</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.428020469705999</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>10.02514117837292</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>7.741403261133382</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>7.541164628721503</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>7.862979394195357</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>9.601725344923166</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7.926869232063749</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>7.550916958062851</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>7.634409984221662</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>9.817577442255841</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7,41; 8,74</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>6,97; 8,28</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,75; 8,04</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9,32; 11,04</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,11; 8,41</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,9; 8,22</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,14; 8,5</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8,99; 10,25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7,44; 8,36</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7,11; 8,03</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7,14; 8,08</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,35; 10,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>7.406946067674546</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>6.970202739102271</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6.745560723861852</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>9.320754702548886</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>7.105292016349196</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>6.899446128972304</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>7.144413710511453</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>8.992436334189772</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>7.438998844064121</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>7.110811785885095</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>7.139625506955259</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>9.347468101027298</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.742891328216873</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.281600510370623</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.042589323062318</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.03653210290481</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>8.407907933704042</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>8.221341031386455</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>8.502114563184433</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>10.25363140925449</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8.364360575132251</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>8.028727323691641</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>8.082358831813474</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>10.43278824947897</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7,73</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,48</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,69</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,08</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,35</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,63</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7,9</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7,3</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7,55</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,2; 8,26</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6,81; 7,77</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7,03; 8,04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9,25; 10,17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,56; 8,57</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,83; 7,85</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,1; 8,12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9,32; 10,36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7,52; 8,25</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6,94; 7,64</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7,18; 7,88</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,39; 10,08</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>7.7255909831622</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7.259802343341669</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7.480943008796895</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9.689708325681822</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>8.084033413315826</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>7.346304927233765</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>7.626837564305053</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>9.803971746929124</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7.897341148471421</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>7.301296505682243</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>7.550998126230817</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.739686209693028</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,45</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,92</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10,21</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,61</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,42</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7,53</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7,48</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>9,95</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>7.202522679661662</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>6.806960879682977</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>7.034749241445901</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>9.251315482694066</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7.559453430173423</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>6.825383873564903</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>7.099850469229381</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>9.324237463077242</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>7.518102709972759</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>6.93749148806739</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>7.18020101943138</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>9.387964780122536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,86; 8,07</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,36; 7,49</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,01; 8,08</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,65; 10,88</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7,0; 8,21</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,5; 7,7</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,84; 7,99</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,15; 10,22</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>7,14; 7,97</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>6,57; 7,38</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>7,06; 7,86</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,57; 10,39</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.256285470545835</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.767169106594174</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.037385848244867</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.16595106957668</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>8.573433979171821</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>7.848533866492647</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>8.122131831459802</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>10.36153432422676</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>8.253199608148369</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>7.635993108184032</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>7.882266508946086</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>10.08196497080323</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,52</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,76</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,29</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,19</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,42</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9,42</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,44</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7,24</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7,59</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,36</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>7.448989380613394</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6.918398463436762</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7.535558132254869</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>10.21426048904296</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>7.614708893455905</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>7.047887738963177</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>7.416441087901015</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>9.675634985309356</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>7.528436446059702</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>6.980887677838897</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>7.477970190373673</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>9.954292970064156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>6,94; 8,02</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6,78; 7,83</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7,18; 8,31</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8,72; 9,8</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 7,88</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,63; 7,73</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6,93; 7,95</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8,86; 10,0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7,04; 7,8</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>6,83; 7,65</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7,25; 7,97</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,97; 9,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.860432538551507</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>6.356548708602413</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>7.008727241066294</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>9.651260370947186</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>7.001374643015895</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>6.504695812058114</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>6.841949889273931</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>9.146220970568574</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7.137973380849234</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>6.574131972016074</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>7.061880110488296</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>9.57414892233931</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.074719445900849</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.493900051714289</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.077220629451459</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.87830727812664</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>8.210194353661993</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7.695346152625976</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>7.994491532576625</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>10.22374772295747</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7.966786585871147</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>7.378456670761565</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>7.855691949969458</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>10.38899789858583</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.516794022213623</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.30231466303038</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>7.763728993710781</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9.294569852596181</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7.363384395784155</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>7.18566392952499</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7.421730836872748</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>9.416920756564643</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7.439815038559527</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>7.243724067223519</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>7.592032926692769</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>9.35533961708447</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>6.936199129830388</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6.776095682495327</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>7.177917730466402</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>8.719327585187735</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>6.799509482679527</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>6.631833012096489</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>6.931017556744941</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>8.857839233185793</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7.037864126621157</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>6.826930084937245</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>7.251506961831164</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>8.967017524749714</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.024388832276648</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.830241389416652</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.310138304742498</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>9.797703887904524</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>7.881486677985167</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7.726381834316602</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>7.947900255197082</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>9.997807004694343</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.799466964172078</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>7.650234506381063</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>7.966780682181282</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>9.737242088110674</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,78</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,27</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7,39; 7,99</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6,97; 7,54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7,3; 7,85</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 10,1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,44; 8,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,96; 7,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,27; 7,87</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9,34; 9,91</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7,48; 7,9</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7,06; 7,45</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7,35; 7,76</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,52; 9,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>7.686503722220882</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7.257644538882922</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7.560752428861319</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>9.780471477728199</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>7.697767415738436</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>7.271810580812661</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>7.564667708404688</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>9.630335428656423</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7.691968349363568</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>7.264523921937828</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>7.562655396620261</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>9.709417831196458</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>7.388847330498332</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>6.967653759609462</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>7.296124518993391</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>9.475469669784273</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>7.435603977477592</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>6.960188731507415</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>7.267688705319162</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>9.338891050971011</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>7.483051501231841</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>7.055665257880269</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>7.347803524329539</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>9.517593386670626</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.987741645299486</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.54324902018594</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.850289141082586</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>10.09525800757605</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8.002345327215043</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>7.554722198807807</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>7.872403767905337</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>9.911925337327148</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7.900606896418965</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>7.452135021602592</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>7.761344036894315</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>9.934697345666024</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
